--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119751168</v>
+        <v>119702254</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2709,14 +2709,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult S 785 m, Ög</t>
+          <t>Skrikhult SSO-S 825 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558701</v>
+        <v>558808</v>
       </c>
       <c r="R19" t="n">
-        <v>6502972</v>
+        <v>6502945</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119702254</v>
+        <v>119702262</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2833,14 +2833,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 825 m, Ög</t>
+          <t>Skrikhult SSO-S 810 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558808</v>
+        <v>558823</v>
       </c>
       <c r="R20" t="n">
-        <v>6502945</v>
+        <v>6502970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119702262</v>
+        <v>119751168</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,14 +2957,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 810 m, Ög</t>
+          <t>Skrikhult S 785 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558823</v>
+        <v>558701</v>
       </c>
       <c r="R21" t="n">
-        <v>6502970</v>
+        <v>6502972</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119702254</v>
+        <v>119751168</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2709,14 +2709,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 825 m, Ög</t>
+          <t>Skrikhult S 785 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558808</v>
+        <v>558701</v>
       </c>
       <c r="R19" t="n">
-        <v>6502945</v>
+        <v>6502972</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119702262</v>
+        <v>119702254</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2833,14 +2833,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 810 m, Ög</t>
+          <t>Skrikhult SSO-S 825 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558823</v>
+        <v>558808</v>
       </c>
       <c r="R20" t="n">
-        <v>6502970</v>
+        <v>6502945</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119751168</v>
+        <v>119702262</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,14 +2957,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikhult S 785 m, Ög</t>
+          <t>Skrikhult SSO-S 810 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558701</v>
+        <v>558823</v>
       </c>
       <c r="R21" t="n">
-        <v>6502972</v>
+        <v>6502970</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119702199</v>
+        <v>119703666</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,54 +1802,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 660 m, Ög</t>
+          <t>Skrikhult SSO 705 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558809</v>
+        <v>558880</v>
       </c>
       <c r="R12" t="n">
-        <v>6503119</v>
+        <v>6503090</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1882,6 +1874,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119710083</v>
+        <v>119710107</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,37 +1923,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2006,6 +1995,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Några få plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119702318</v>
+        <v>119710083</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2073,7 +2067,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2090,14 +2084,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skrikhult S 645 m, Ög</t>
+          <t>Skrikhult SSO-S 675 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558720</v>
+        <v>558847</v>
       </c>
       <c r="R14" t="n">
-        <v>6503119</v>
+        <v>6503113</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2162,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119703666</v>
+        <v>119702199</v>
       </c>
       <c r="B15" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,46 +2168,54 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 705 m, Ög</t>
+          <t>Skrikhult SSO-S 660 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558880</v>
+        <v>558809</v>
       </c>
       <c r="R15" t="n">
-        <v>6503090</v>
+        <v>6503119</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,11 +2248,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119710107</v>
+        <v>119702318</v>
       </c>
       <c r="B16" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,29 +2292,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2327,14 +2332,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 675 m, Ög</t>
+          <t>Skrikhult S 645 m, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558847</v>
+        <v>558720</v>
       </c>
       <c r="R16" t="n">
-        <v>6503113</v>
+        <v>6503119</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2367,11 +2372,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Några få plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2533,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119702222</v>
+        <v>119702254</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2578,24 +2578,24 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrikhult S 690 m, Ög</t>
+          <t>Skrikhult SSO-S 825 m, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558686</v>
+        <v>558808</v>
       </c>
       <c r="R18" t="n">
-        <v>6503070</v>
+        <v>6502945</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119751168</v>
+        <v>119702262</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2709,14 +2709,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult S 785 m, Ög</t>
+          <t>Skrikhult SSO-S 810 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558701</v>
+        <v>558823</v>
       </c>
       <c r="R19" t="n">
-        <v>6502972</v>
+        <v>6502970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119702254</v>
+        <v>119751168</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2833,14 +2833,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 825 m, Ög</t>
+          <t>Skrikhult S 785 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558808</v>
+        <v>558701</v>
       </c>
       <c r="R20" t="n">
-        <v>6502945</v>
+        <v>6502972</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119702262</v>
+        <v>119702222</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2950,24 +2950,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 810 m, Ög</t>
+          <t>Skrikhult S 690 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558823</v>
+        <v>558686</v>
       </c>
       <c r="R21" t="n">
-        <v>6502970</v>
+        <v>6503070</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119825623</v>
+        <v>119825611</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3334,17 +3334,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 780 m, Ög</t>
+          <t>Skrikhult SSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558951</v>
+        <v>558952</v>
       </c>
       <c r="R24" t="n">
-        <v>6503018</v>
+        <v>6503001</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119825611</v>
+        <v>119825623</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3458,17 +3458,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 805 m, Ög</t>
+          <t>Skrikhult SSO 780 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558952</v>
+        <v>558951</v>
       </c>
       <c r="R25" t="n">
-        <v>6503001</v>
+        <v>6503018</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119832201</v>
+        <v>119834421</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3582,17 +3582,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 760 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558855</v>
+        <v>558820</v>
       </c>
       <c r="R26" t="n">
-        <v>6503015</v>
+        <v>6503011</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834421</v>
+        <v>119832201</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,17 +3830,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult SSO-S 760 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558820</v>
+        <v>558855</v>
       </c>
       <c r="R28" t="n">
-        <v>6503011</v>
+        <v>6503015</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119876386</v>
+        <v>119876379</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4078,14 +4078,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558812</v>
+        <v>558791</v>
       </c>
       <c r="R30" t="n">
-        <v>6503062</v>
+        <v>6503087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119876406</v>
+        <v>119875598</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4162,35 +4162,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4202,14 +4202,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558907</v>
+        <v>558757</v>
       </c>
       <c r="R31" t="n">
-        <v>6503088</v>
+        <v>6503043</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4242,6 +4242,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4274,10 +4279,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875598</v>
+        <v>119875457</v>
       </c>
       <c r="B32" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4286,57 +4291,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558757</v>
+        <v>558718</v>
       </c>
       <c r="R32" t="n">
-        <v>6503043</v>
+        <v>6503026</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4370,7 +4375,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 50 plantor</t>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4403,7 +4408,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876427</v>
+        <v>119876386</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4438,7 +4443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4455,17 +4460,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558979</v>
+        <v>558812</v>
       </c>
       <c r="R33" t="n">
-        <v>6503050</v>
+        <v>6503062</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4527,7 +4532,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119876379</v>
+        <v>119876406</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4562,7 +4567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4572,21 +4577,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558791</v>
+        <v>558907</v>
       </c>
       <c r="R34" t="n">
-        <v>6503087</v>
+        <v>6503088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4651,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875457</v>
+        <v>119876427</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4686,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4703,14 +4708,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558718</v>
+        <v>558979</v>
       </c>
       <c r="R35" t="n">
-        <v>6503026</v>
+        <v>6503050</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4743,11 +4748,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4780,10 +4780,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119918419</v>
+        <v>119751705</v>
       </c>
       <c r="B36" t="n">
-        <v>94681</v>
+        <v>105009</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4796,41 +4796,53 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558834</v>
+        <v>558794</v>
       </c>
       <c r="R36" t="n">
-        <v>6503110</v>
+        <v>6502975</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4854,12 +4866,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4875,11 +4887,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4897,7 +4904,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918403</v>
+        <v>119918537</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4932,7 +4939,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4942,24 +4949,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558834</v>
+        <v>558947</v>
       </c>
       <c r="R37" t="n">
-        <v>6503110</v>
+        <v>6503121</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5004,11 +5011,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5026,7 +5028,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918375</v>
+        <v>119918328</v>
       </c>
       <c r="B38" t="n">
         <v>97907</v>
@@ -5061,7 +5063,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5078,14 +5080,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558786</v>
+        <v>558801</v>
       </c>
       <c r="R38" t="n">
-        <v>6503023</v>
+        <v>6502991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5133,11 +5135,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5155,7 +5152,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119918328</v>
+        <v>119918403</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -5200,21 +5197,21 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558801</v>
+        <v>558834</v>
       </c>
       <c r="R39" t="n">
-        <v>6502991</v>
+        <v>6503110</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5262,6 +5259,11 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5279,7 +5281,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119918517</v>
+        <v>119875436</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -5314,7 +5316,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5331,14 +5333,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558861</v>
+        <v>558732</v>
       </c>
       <c r="R40" t="n">
-        <v>6503130</v>
+        <v>6502967</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5365,12 +5367,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5403,10 +5405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119751705</v>
+        <v>119918375</v>
       </c>
       <c r="B41" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5415,35 +5417,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5455,17 +5457,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558794</v>
+        <v>558786</v>
       </c>
       <c r="R41" t="n">
-        <v>6502975</v>
+        <v>6503023</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5489,12 +5491,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5510,6 +5512,11 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5527,7 +5534,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918537</v>
+        <v>119918517</v>
       </c>
       <c r="B42" t="n">
         <v>97907</v>
@@ -5562,7 +5569,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5572,24 +5579,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558947</v>
+        <v>558861</v>
       </c>
       <c r="R42" t="n">
-        <v>6503121</v>
+        <v>6503130</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5651,10 +5658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119875436</v>
+        <v>119918419</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5663,54 +5670,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558732</v>
+        <v>558834</v>
       </c>
       <c r="R43" t="n">
-        <v>6502967</v>
+        <v>6503110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5737,12 +5732,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5758,6 +5753,11 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119964682</v>
+        <v>119966290</v>
       </c>
       <c r="B44" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,49 +5787,54 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558954</v>
+        <v>559102</v>
       </c>
       <c r="R44" t="n">
-        <v>6503037</v>
+        <v>6502963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6018,10 +6023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966118</v>
+        <v>119964682</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6030,57 +6035,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>559095</v>
+        <v>558954</v>
       </c>
       <c r="R46" t="n">
-        <v>6502991</v>
+        <v>6503037</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966290</v>
+        <v>119966118</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6187,24 +6187,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559102</v>
+        <v>559095</v>
       </c>
       <c r="R47" t="n">
-        <v>6502963</v>
+        <v>6502991</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964711</v>
+        <v>119966093</v>
       </c>
       <c r="B49" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,35 +6407,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6447,17 +6447,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558933</v>
+        <v>559098</v>
       </c>
       <c r="R49" t="n">
-        <v>6503091</v>
+        <v>6503022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966093</v>
+        <v>119964711</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>559098</v>
+        <v>558933</v>
       </c>
       <c r="R50" t="n">
-        <v>6503022</v>
+        <v>6503091</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119703666</v>
+        <v>119702318</v>
       </c>
       <c r="B12" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,46 +1802,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 705 m, Ög</t>
+          <t>Skrikhult S 645 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558880</v>
+        <v>558720</v>
       </c>
       <c r="R12" t="n">
-        <v>6503090</v>
+        <v>6503119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,11 +1882,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119710107</v>
+        <v>119703666</v>
       </c>
       <c r="B13" t="n">
         <v>105009</v>
@@ -1948,21 +1951,21 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 675 m, Ög</t>
+          <t>Skrikhult SSO 705 m, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558847</v>
+        <v>558880</v>
       </c>
       <c r="R13" t="n">
-        <v>6503113</v>
+        <v>6503090</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1999,7 +2002,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några få plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2156,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119702199</v>
+        <v>119710107</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,37 +2171,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2208,14 +2203,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 660 m, Ög</t>
+          <t>Skrikhult SSO-S 675 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558809</v>
+        <v>558847</v>
       </c>
       <c r="R15" t="n">
-        <v>6503119</v>
+        <v>6503113</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,6 +2243,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Några få plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119702318</v>
+        <v>119702123</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2332,14 +2332,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrikhult S 645 m, Ög</t>
+          <t>Skrikhult SSO 705 m, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558720</v>
+        <v>558880</v>
       </c>
       <c r="R16" t="n">
-        <v>6503119</v>
+        <v>6503090</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2372,6 +2372,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Något spridd på lokalen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,7 +2409,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119702123</v>
+        <v>119702199</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2456,14 +2461,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 705 m, Ög</t>
+          <t>Skrikhult SSO-S 660 m, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558880</v>
+        <v>558809</v>
       </c>
       <c r="R17" t="n">
-        <v>6503090</v>
+        <v>6503119</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2496,11 +2501,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Något spridd på lokalen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119702262</v>
+        <v>119702222</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,24 +2702,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 810 m, Ög</t>
+          <t>Skrikhult S 690 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558823</v>
+        <v>558686</v>
       </c>
       <c r="R19" t="n">
-        <v>6502970</v>
+        <v>6503070</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119702222</v>
+        <v>119702262</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2950,24 +2950,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikhult S 690 m, Ög</t>
+          <t>Skrikhult SSO-S 810 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558686</v>
+        <v>558823</v>
       </c>
       <c r="R21" t="n">
-        <v>6503070</v>
+        <v>6502970</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825673</v>
+        <v>119825623</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 790 m, Ög</t>
+          <t>Skrikhult SSO 780 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558897</v>
+        <v>558951</v>
       </c>
       <c r="R22" t="n">
-        <v>6502998</v>
+        <v>6503018</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,11 +3121,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,7 +3153,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119825631</v>
+        <v>119825673</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3193,7 +3188,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3203,24 +3198,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 760 m, Ög</t>
+          <t>Skrikhult SSO-S 790 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558919</v>
+        <v>558897</v>
       </c>
       <c r="R23" t="n">
-        <v>6503036</v>
+        <v>6502998</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3250,6 +3245,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119825623</v>
+        <v>119825631</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3458,14 +3458,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 780 m, Ög</t>
+          <t>Skrikhult SSO 760 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558951</v>
+        <v>558919</v>
       </c>
       <c r="R25" t="n">
-        <v>6503018</v>
+        <v>6503036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834421</v>
+        <v>119832201</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3582,17 +3582,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult SSO-S 760 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558820</v>
+        <v>558855</v>
       </c>
       <c r="R26" t="n">
-        <v>6503011</v>
+        <v>6503015</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834482</v>
+        <v>119834539</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3706,14 +3706,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skrikhult S 770 m, Ög</t>
+          <t>Skrikhult S 795 m, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558820</v>
+        <v>558829</v>
       </c>
       <c r="R27" t="n">
-        <v>6502998</v>
+        <v>6502974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119832201</v>
+        <v>119834482</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,17 +3830,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 760 m, Ög</t>
+          <t>Skrikhult S 770 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558855</v>
+        <v>558820</v>
       </c>
       <c r="R28" t="n">
-        <v>6503015</v>
+        <v>6502998</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834539</v>
+        <v>119834421</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3954,14 +3954,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrikhult S 795 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558829</v>
+        <v>558820</v>
       </c>
       <c r="R29" t="n">
-        <v>6502974</v>
+        <v>6503011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875598</v>
+        <v>119876427</v>
       </c>
       <c r="B31" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4162,57 +4162,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558757</v>
+        <v>558979</v>
       </c>
       <c r="R31" t="n">
-        <v>6503043</v>
+        <v>6503050</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4242,11 +4242,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4408,7 +4403,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876386</v>
+        <v>119876406</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4443,7 +4438,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4453,21 +4448,21 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558812</v>
+        <v>558907</v>
       </c>
       <c r="R33" t="n">
-        <v>6503062</v>
+        <v>6503088</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4532,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119876406</v>
+        <v>119875598</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4544,35 +4539,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4584,14 +4579,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558907</v>
+        <v>558757</v>
       </c>
       <c r="R34" t="n">
-        <v>6503088</v>
+        <v>6503043</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4624,6 +4619,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876427</v>
+        <v>119876386</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4708,17 +4708,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558979</v>
+        <v>558812</v>
       </c>
       <c r="R35" t="n">
-        <v>6503050</v>
+        <v>6503062</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119751705</v>
+        <v>119918419</v>
       </c>
       <c r="B36" t="n">
-        <v>105009</v>
+        <v>94681</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4796,53 +4796,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558794</v>
+        <v>558834</v>
       </c>
       <c r="R36" t="n">
-        <v>6502975</v>
+        <v>6503110</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4866,12 +4854,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,6 +4875,11 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4904,7 +4897,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918537</v>
+        <v>119918517</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4939,7 +4932,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4949,24 +4942,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558947</v>
+        <v>558861</v>
       </c>
       <c r="R37" t="n">
-        <v>6503121</v>
+        <v>6503130</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5028,7 +5021,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918328</v>
+        <v>119918537</v>
       </c>
       <c r="B38" t="n">
         <v>97907</v>
@@ -5063,7 +5056,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5080,17 +5073,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558801</v>
+        <v>558947</v>
       </c>
       <c r="R38" t="n">
-        <v>6502991</v>
+        <v>6503121</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5152,7 +5145,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119918403</v>
+        <v>119875436</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -5187,7 +5180,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5204,14 +5197,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558834</v>
+        <v>558732</v>
       </c>
       <c r="R39" t="n">
-        <v>6503110</v>
+        <v>6502967</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5238,12 +5231,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5259,11 +5252,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5281,7 +5269,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875436</v>
+        <v>119918328</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -5316,7 +5304,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5326,21 +5314,21 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558732</v>
+        <v>558801</v>
       </c>
       <c r="R40" t="n">
-        <v>6502967</v>
+        <v>6502991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5367,12 +5355,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5534,10 +5522,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918517</v>
+        <v>119751705</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5546,57 +5534,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558861</v>
+        <v>558794</v>
       </c>
       <c r="R42" t="n">
-        <v>6503130</v>
+        <v>6502975</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5620,12 +5608,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5658,10 +5646,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918419</v>
+        <v>119918403</v>
       </c>
       <c r="B43" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5670,30 +5658,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966290</v>
+        <v>119964682</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,54 +5787,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559102</v>
+        <v>558954</v>
       </c>
       <c r="R44" t="n">
-        <v>6502963</v>
+        <v>6503037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5899,7 +5894,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119964721</v>
+        <v>119966093</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5934,7 +5929,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5951,17 +5946,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558950</v>
+        <v>559098</v>
       </c>
       <c r="R45" t="n">
-        <v>6503096</v>
+        <v>6503022</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6023,10 +6018,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119964682</v>
+        <v>119964704</v>
       </c>
       <c r="B46" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6035,25 +6030,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6063,21 +6058,26 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558954</v>
+        <v>558933</v>
       </c>
       <c r="R46" t="n">
-        <v>6503037</v>
+        <v>6503091</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6110,6 +6110,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6142,7 +6147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966118</v>
+        <v>119966290</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -6177,7 +6182,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6187,24 +6192,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559095</v>
+        <v>559102</v>
       </c>
       <c r="R47" t="n">
-        <v>6502991</v>
+        <v>6502963</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6266,10 +6271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964704</v>
+        <v>119964711</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6278,35 +6283,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6358,11 +6363,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6395,7 +6395,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966093</v>
+        <v>119964721</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6447,17 +6447,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559098</v>
+        <v>558950</v>
       </c>
       <c r="R49" t="n">
-        <v>6503022</v>
+        <v>6503096</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119964711</v>
+        <v>119966118</v>
       </c>
       <c r="B50" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558933</v>
+        <v>559095</v>
       </c>
       <c r="R50" t="n">
-        <v>6503091</v>
+        <v>6502991</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119702318</v>
+        <v>119703666</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,54 +1802,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skrikhult S 645 m, Ög</t>
+          <t>Skrikhult SSO 705 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558720</v>
+        <v>558880</v>
       </c>
       <c r="R12" t="n">
-        <v>6503119</v>
+        <v>6503090</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1882,6 +1874,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119703666</v>
+        <v>119702123</v>
       </c>
       <c r="B13" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,32 +1923,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Något spridd på lokalen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,7 +2040,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119710083</v>
+        <v>119702318</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2070,7 +2075,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2087,14 +2092,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 675 m, Ög</t>
+          <t>Skrikhult S 645 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558847</v>
+        <v>558720</v>
       </c>
       <c r="R14" t="n">
-        <v>6503113</v>
+        <v>6503119</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2280,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119702123</v>
+        <v>119702199</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2315,7 +2320,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2332,14 +2337,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 705 m, Ög</t>
+          <t>Skrikhult SSO-S 660 m, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558880</v>
+        <v>558809</v>
       </c>
       <c r="R16" t="n">
-        <v>6503090</v>
+        <v>6503119</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2372,11 +2377,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Något spridd på lokalen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119702199</v>
+        <v>119710083</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2461,14 +2461,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 660 m, Ög</t>
+          <t>Skrikhult SSO-S 675 m, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558809</v>
+        <v>558847</v>
       </c>
       <c r="R17" t="n">
-        <v>6503119</v>
+        <v>6503113</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119702254</v>
+        <v>119702262</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2585,14 +2585,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 825 m, Ög</t>
+          <t>Skrikhult SSO-S 810 m, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558808</v>
+        <v>558823</v>
       </c>
       <c r="R18" t="n">
-        <v>6502945</v>
+        <v>6502970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119702222</v>
+        <v>119702254</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,24 +2702,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult S 690 m, Ög</t>
+          <t>Skrikhult SSO-S 825 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558686</v>
+        <v>558808</v>
       </c>
       <c r="R19" t="n">
-        <v>6503070</v>
+        <v>6502945</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119751168</v>
+        <v>119702222</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2826,24 +2826,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikhult S 785 m, Ög</t>
+          <t>Skrikhult S 690 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558701</v>
+        <v>558686</v>
       </c>
       <c r="R20" t="n">
-        <v>6502972</v>
+        <v>6503070</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119702262</v>
+        <v>119751168</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,14 +2957,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 810 m, Ög</t>
+          <t>Skrikhult S 785 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558823</v>
+        <v>558701</v>
       </c>
       <c r="R21" t="n">
-        <v>6502970</v>
+        <v>6502972</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825623</v>
+        <v>119825611</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3081,17 +3081,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 780 m, Ög</t>
+          <t>Skrikhult SSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558951</v>
+        <v>558952</v>
       </c>
       <c r="R22" t="n">
-        <v>6503018</v>
+        <v>6503001</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119825673</v>
+        <v>119825623</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3198,24 +3198,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 790 m, Ög</t>
+          <t>Skrikhult SSO 780 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558897</v>
+        <v>558951</v>
       </c>
       <c r="R23" t="n">
-        <v>6502998</v>
+        <v>6503018</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3245,11 +3245,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,7 +3277,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119825611</v>
+        <v>119825631</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3317,7 +3312,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3334,17 +3329,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 805 m, Ög</t>
+          <t>Skrikhult SSO 760 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558952</v>
+        <v>558919</v>
       </c>
       <c r="R24" t="n">
-        <v>6503001</v>
+        <v>6503036</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3406,7 +3401,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119825631</v>
+        <v>119825673</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3441,7 +3436,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3451,24 +3446,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 760 m, Ög</t>
+          <t>Skrikhult SSO-S 790 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558919</v>
+        <v>558897</v>
       </c>
       <c r="R25" t="n">
-        <v>6503036</v>
+        <v>6502998</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3498,6 +3493,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119832201</v>
+        <v>119834482</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3582,17 +3582,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 760 m, Ög</t>
+          <t>Skrikhult S 770 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558855</v>
+        <v>558820</v>
       </c>
       <c r="R26" t="n">
-        <v>6503015</v>
+        <v>6502998</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834539</v>
+        <v>119832201</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3706,17 +3706,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skrikhult S 795 m, Ög</t>
+          <t>Skrikhult SSO-S 760 m, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558829</v>
+        <v>558855</v>
       </c>
       <c r="R27" t="n">
-        <v>6502974</v>
+        <v>6503015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834482</v>
+        <v>119834421</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,14 +3830,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult S 770 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>558820</v>
       </c>
       <c r="R28" t="n">
-        <v>6502998</v>
+        <v>6503011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834421</v>
+        <v>119834539</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3954,14 +3954,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult S 795 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558820</v>
+        <v>558829</v>
       </c>
       <c r="R29" t="n">
-        <v>6503011</v>
+        <v>6502974</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119876379</v>
+        <v>119875598</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4038,54 +4038,54 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558791</v>
+        <v>558757</v>
       </c>
       <c r="R30" t="n">
-        <v>6503087</v>
+        <v>6503043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4118,6 +4118,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4274,7 +4279,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875457</v>
+        <v>119876379</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4309,7 +4314,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4326,17 +4331,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558718</v>
+        <v>558791</v>
       </c>
       <c r="R32" t="n">
-        <v>6503026</v>
+        <v>6503087</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4366,11 +4371,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875598</v>
+        <v>119875457</v>
       </c>
       <c r="B34" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4539,57 +4539,57 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558757</v>
+        <v>558718</v>
       </c>
       <c r="R34" t="n">
-        <v>6503043</v>
+        <v>6503026</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 50 plantor</t>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4897,7 +4897,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918517</v>
+        <v>119918537</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558861</v>
+        <v>558947</v>
       </c>
       <c r="R37" t="n">
-        <v>6503130</v>
+        <v>6503121</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918537</v>
+        <v>119875436</v>
       </c>
       <c r="B38" t="n">
         <v>97907</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5066,24 +5066,24 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558947</v>
+        <v>558732</v>
       </c>
       <c r="R38" t="n">
-        <v>6503121</v>
+        <v>6502967</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5107,12 +5107,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5145,7 +5145,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875436</v>
+        <v>119918403</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5197,14 +5197,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558732</v>
+        <v>558834</v>
       </c>
       <c r="R39" t="n">
-        <v>6502967</v>
+        <v>6503110</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5252,6 +5252,11 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5269,7 +5274,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119918328</v>
+        <v>119918375</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -5304,7 +5309,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5321,14 +5326,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558801</v>
+        <v>558786</v>
       </c>
       <c r="R40" t="n">
-        <v>6502991</v>
+        <v>6503023</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5376,6 +5381,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5393,7 +5403,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918375</v>
+        <v>119918328</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -5428,7 +5438,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5445,14 +5455,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558786</v>
+        <v>558801</v>
       </c>
       <c r="R41" t="n">
-        <v>6503023</v>
+        <v>6502991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5500,11 +5510,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5646,7 +5651,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918403</v>
+        <v>119918517</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5698,14 +5703,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558834</v>
+        <v>558861</v>
       </c>
       <c r="R43" t="n">
-        <v>6503110</v>
+        <v>6503130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5753,11 +5758,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119964682</v>
+        <v>119966118</v>
       </c>
       <c r="B44" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,52 +5787,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558954</v>
+        <v>559095</v>
       </c>
       <c r="R44" t="n">
-        <v>6503037</v>
+        <v>6502991</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5894,7 +5899,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966093</v>
+        <v>119966290</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5929,7 +5934,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5939,24 +5944,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559098</v>
+        <v>559102</v>
       </c>
       <c r="R45" t="n">
-        <v>6503022</v>
+        <v>6502963</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6018,10 +6023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119964704</v>
+        <v>119964682</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6030,25 +6035,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6058,26 +6063,21 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558933</v>
+        <v>558954</v>
       </c>
       <c r="R46" t="n">
-        <v>6503091</v>
+        <v>6503037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6110,11 +6110,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6147,7 +6142,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966290</v>
+        <v>119964721</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -6182,7 +6177,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6192,21 +6187,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559102</v>
+        <v>558950</v>
       </c>
       <c r="R47" t="n">
-        <v>6502963</v>
+        <v>6503096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6271,10 +6266,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964711</v>
+        <v>119964704</v>
       </c>
       <c r="B48" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6283,35 +6278,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6363,6 +6358,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6395,7 +6395,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964721</v>
+        <v>119966093</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6447,17 +6447,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558950</v>
+        <v>559098</v>
       </c>
       <c r="R49" t="n">
-        <v>6503096</v>
+        <v>6503022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966118</v>
+        <v>119964711</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>559095</v>
+        <v>558933</v>
       </c>
       <c r="R50" t="n">
-        <v>6502991</v>
+        <v>6503091</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>119702262</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119702254</v>
+        <v>119702222</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,24 +2702,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 825 m, Ög</t>
+          <t>Skrikhult S 690 m, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558808</v>
+        <v>558686</v>
       </c>
       <c r="R19" t="n">
-        <v>6502945</v>
+        <v>6503070</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119702222</v>
+        <v>119702254</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2826,24 +2826,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikhult S 690 m, Ög</t>
+          <t>Skrikhult SSO-S 825 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558686</v>
+        <v>558808</v>
       </c>
       <c r="R20" t="n">
-        <v>6503070</v>
+        <v>6502945</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>119751168</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825611</v>
+        <v>119825623</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3081,17 +3081,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 805 m, Ög</t>
+          <t>Skrikhult SSO 780 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558952</v>
+        <v>558951</v>
       </c>
       <c r="R22" t="n">
-        <v>6503001</v>
+        <v>6503018</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119825623</v>
+        <v>119825611</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3205,17 +3205,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 780 m, Ög</t>
+          <t>Skrikhult SSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558951</v>
+        <v>558952</v>
       </c>
       <c r="R23" t="n">
-        <v>6503018</v>
+        <v>6503001</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>119825631</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>119825673</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>119834482</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>119832201</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834421</v>
+        <v>119834539</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,14 +3830,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult S 795 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558820</v>
+        <v>558829</v>
       </c>
       <c r="R28" t="n">
-        <v>6503011</v>
+        <v>6502974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834539</v>
+        <v>119834421</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3954,14 +3954,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrikhult S 795 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558829</v>
+        <v>558820</v>
       </c>
       <c r="R29" t="n">
-        <v>6502974</v>
+        <v>6503011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875598</v>
+        <v>119875457</v>
       </c>
       <c r="B30" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4038,57 +4038,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558757</v>
+        <v>558718</v>
       </c>
       <c r="R30" t="n">
-        <v>6503043</v>
+        <v>6503026</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ca 50 plantor</t>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119876427</v>
+        <v>119875598</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>105032</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4167,57 +4167,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558979</v>
+        <v>558757</v>
       </c>
       <c r="R31" t="n">
-        <v>6503050</v>
+        <v>6503043</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4247,6 +4247,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4279,10 +4284,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119876379</v>
+        <v>119876427</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4314,7 +4319,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4331,17 +4336,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558791</v>
+        <v>558979</v>
       </c>
       <c r="R32" t="n">
-        <v>6503087</v>
+        <v>6503050</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876406</v>
+        <v>119876386</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4438,7 +4443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4448,21 +4453,21 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558907</v>
+        <v>558812</v>
       </c>
       <c r="R33" t="n">
-        <v>6503088</v>
+        <v>6503062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4527,10 +4532,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875457</v>
+        <v>119876406</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4562,7 +4567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4572,24 +4577,24 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558718</v>
+        <v>558907</v>
       </c>
       <c r="R34" t="n">
-        <v>6503026</v>
+        <v>6503088</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4619,11 +4624,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876386</v>
+        <v>119876379</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4708,14 +4708,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558812</v>
+        <v>558791</v>
       </c>
       <c r="R35" t="n">
-        <v>6503062</v>
+        <v>6503087</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119918419</v>
+        <v>119918517</v>
       </c>
       <c r="B36" t="n">
-        <v>94681</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4792,42 +4792,54 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558834</v>
+        <v>558861</v>
       </c>
       <c r="R36" t="n">
-        <v>6503110</v>
+        <v>6503130</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4875,11 +4887,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4900,7 +4907,7 @@
         <v>119918537</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5021,10 +5028,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875436</v>
+        <v>119751705</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>105032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5033,57 +5040,57 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558732</v>
+        <v>558794</v>
       </c>
       <c r="R38" t="n">
-        <v>6502967</v>
+        <v>6502975</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5107,12 +5114,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5145,10 +5152,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119918403</v>
+        <v>119875436</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5180,7 +5187,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5197,14 +5204,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558834</v>
+        <v>558732</v>
       </c>
       <c r="R39" t="n">
-        <v>6503110</v>
+        <v>6502967</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5231,12 +5238,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5252,11 +5259,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5277,7 +5279,7 @@
         <v>119918375</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5403,10 +5405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918328</v>
+        <v>119918419</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>94704</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5415,54 +5417,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558801</v>
+        <v>558834</v>
       </c>
       <c r="R41" t="n">
-        <v>6502991</v>
+        <v>6503110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5510,6 +5500,11 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119751705</v>
+        <v>119918403</v>
       </c>
       <c r="B42" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5539,57 +5534,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558794</v>
+        <v>558834</v>
       </c>
       <c r="R42" t="n">
-        <v>6502975</v>
+        <v>6503110</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5613,12 +5608,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5634,6 +5629,11 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918517</v>
+        <v>119918328</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5696,21 +5696,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558861</v>
+        <v>558801</v>
       </c>
       <c r="R43" t="n">
-        <v>6503130</v>
+        <v>6502991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966118</v>
+        <v>119966093</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5827,14 +5827,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559095</v>
+        <v>559098</v>
       </c>
       <c r="R44" t="n">
-        <v>6502991</v>
+        <v>6503022</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966290</v>
+        <v>119966118</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5944,24 +5944,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559102</v>
+        <v>559095</v>
       </c>
       <c r="R45" t="n">
-        <v>6502963</v>
+        <v>6502991</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119964682</v>
+        <v>119966290</v>
       </c>
       <c r="B46" t="n">
-        <v>91185</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6035,49 +6035,54 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558954</v>
+        <v>559102</v>
       </c>
       <c r="R46" t="n">
-        <v>6503037</v>
+        <v>6502963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6142,10 +6147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119964721</v>
+        <v>119964711</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>105032</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6154,35 +6159,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6194,14 +6199,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558950</v>
+        <v>558933</v>
       </c>
       <c r="R47" t="n">
-        <v>6503096</v>
+        <v>6503091</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6266,10 +6271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964704</v>
+        <v>119964721</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6318,14 +6323,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558933</v>
+        <v>558950</v>
       </c>
       <c r="R48" t="n">
-        <v>6503091</v>
+        <v>6503096</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6358,11 +6363,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966093</v>
+        <v>119964682</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>91203</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,57 +6407,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559098</v>
+        <v>558954</v>
       </c>
       <c r="R49" t="n">
-        <v>6503022</v>
+        <v>6503037</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6514,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119964711</v>
+        <v>119964704</v>
       </c>
       <c r="B50" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6526,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6611,6 +6606,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -3153,7 +3153,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119825611</v>
+        <v>119825631</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3205,17 +3205,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 805 m, Ög</t>
+          <t>Skrikhult SSO 760 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558952</v>
+        <v>558919</v>
       </c>
       <c r="R23" t="n">
-        <v>6503001</v>
+        <v>6503036</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119825631</v>
+        <v>119825611</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3329,17 +3329,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 760 m, Ög</t>
+          <t>Skrikhult SSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558919</v>
+        <v>558952</v>
       </c>
       <c r="R24" t="n">
-        <v>6503036</v>
+        <v>6503001</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834482</v>
+        <v>119832201</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3582,17 +3582,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrikhult S 770 m, Ög</t>
+          <t>Skrikhult SSO-S 760 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558820</v>
+        <v>558855</v>
       </c>
       <c r="R26" t="n">
-        <v>6502998</v>
+        <v>6503015</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119832201</v>
+        <v>119834539</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3706,17 +3706,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 760 m, Ög</t>
+          <t>Skrikhult S 795 m, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558855</v>
+        <v>558829</v>
       </c>
       <c r="R27" t="n">
-        <v>6503015</v>
+        <v>6502974</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834539</v>
+        <v>119834421</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,14 +3830,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult S 795 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558829</v>
+        <v>558820</v>
       </c>
       <c r="R28" t="n">
-        <v>6502974</v>
+        <v>6503011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834421</v>
+        <v>119834482</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3954,14 +3954,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult S 770 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>558820</v>
       </c>
       <c r="R29" t="n">
-        <v>6503011</v>
+        <v>6502998</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875457</v>
+        <v>119876427</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4078,14 +4078,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558718</v>
+        <v>558979</v>
       </c>
       <c r="R30" t="n">
-        <v>6503026</v>
+        <v>6503050</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4118,11 +4118,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4155,10 +4150,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875598</v>
+        <v>119875457</v>
       </c>
       <c r="B31" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4167,57 +4162,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558757</v>
+        <v>558718</v>
       </c>
       <c r="R31" t="n">
-        <v>6503043</v>
+        <v>6503026</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4251,7 +4246,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ca 50 plantor</t>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4284,7 +4279,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119876427</v>
+        <v>119876406</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4319,7 +4314,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4329,24 +4324,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558979</v>
+        <v>558907</v>
       </c>
       <c r="R32" t="n">
-        <v>6503050</v>
+        <v>6503088</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876386</v>
+        <v>119875598</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4420,54 +4415,54 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558812</v>
+        <v>558757</v>
       </c>
       <c r="R33" t="n">
-        <v>6503062</v>
+        <v>6503043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4500,6 +4495,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4532,7 +4532,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119876406</v>
+        <v>119876379</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4577,21 +4577,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558907</v>
+        <v>558791</v>
       </c>
       <c r="R34" t="n">
-        <v>6503088</v>
+        <v>6503087</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876379</v>
+        <v>119876386</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4708,14 +4708,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558791</v>
+        <v>558812</v>
       </c>
       <c r="R35" t="n">
-        <v>6503087</v>
+        <v>6503062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119918517</v>
+        <v>119875436</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4832,14 +4832,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558861</v>
+        <v>558732</v>
       </c>
       <c r="R36" t="n">
-        <v>6503130</v>
+        <v>6502967</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4904,10 +4904,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918537</v>
+        <v>119918419</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4916,57 +4916,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558947</v>
+        <v>558834</v>
       </c>
       <c r="R37" t="n">
-        <v>6503121</v>
+        <v>6503110</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5011,6 +4999,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5028,10 +5021,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119751705</v>
+        <v>119918403</v>
       </c>
       <c r="B38" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5040,57 +5033,57 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558794</v>
+        <v>558834</v>
       </c>
       <c r="R38" t="n">
-        <v>6502975</v>
+        <v>6503110</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5114,12 +5107,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5135,6 +5128,11 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5152,7 +5150,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875436</v>
+        <v>119918328</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -5187,7 +5185,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5197,21 +5195,21 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558732</v>
+        <v>558801</v>
       </c>
       <c r="R39" t="n">
-        <v>6502967</v>
+        <v>6502991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5238,12 +5236,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5405,10 +5403,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918419</v>
+        <v>119751705</v>
       </c>
       <c r="B41" t="n">
-        <v>94704</v>
+        <v>105032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5421,41 +5419,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558834</v>
+        <v>558794</v>
       </c>
       <c r="R41" t="n">
-        <v>6503110</v>
+        <v>6502975</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5479,12 +5489,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5500,11 +5510,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5522,7 +5527,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918403</v>
+        <v>119918517</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5574,14 +5579,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558834</v>
+        <v>558861</v>
       </c>
       <c r="R42" t="n">
-        <v>6503110</v>
+        <v>6503130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5629,11 +5634,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918328</v>
+        <v>119918537</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5703,17 +5703,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558801</v>
+        <v>558947</v>
       </c>
       <c r="R43" t="n">
-        <v>6502991</v>
+        <v>6503121</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966093</v>
+        <v>119964704</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5827,17 +5827,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559098</v>
+        <v>558933</v>
       </c>
       <c r="R44" t="n">
-        <v>6503022</v>
+        <v>6503091</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5867,6 +5867,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5899,7 +5904,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966118</v>
+        <v>119964721</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5934,7 +5939,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5951,17 +5956,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559095</v>
+        <v>558950</v>
       </c>
       <c r="R45" t="n">
-        <v>6502991</v>
+        <v>6503096</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6023,7 +6028,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966290</v>
+        <v>119966093</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -6058,7 +6063,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6068,24 +6073,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>559102</v>
+        <v>559098</v>
       </c>
       <c r="R46" t="n">
-        <v>6502963</v>
+        <v>6503022</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6147,10 +6152,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119964711</v>
+        <v>119964682</v>
       </c>
       <c r="B47" t="n">
-        <v>105032</v>
+        <v>91203</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6163,50 +6168,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558933</v>
+        <v>558954</v>
       </c>
       <c r="R47" t="n">
-        <v>6503091</v>
+        <v>6503037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964721</v>
+        <v>119964711</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6283,35 +6283,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6323,14 +6323,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558950</v>
+        <v>558933</v>
       </c>
       <c r="R48" t="n">
-        <v>6503096</v>
+        <v>6503091</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964682</v>
+        <v>119966290</v>
       </c>
       <c r="B49" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,49 +6407,54 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558954</v>
+        <v>559102</v>
       </c>
       <c r="R49" t="n">
-        <v>6503037</v>
+        <v>6502963</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6514,7 +6519,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119964704</v>
+        <v>119966118</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -6549,7 +6554,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6566,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558933</v>
+        <v>559095</v>
       </c>
       <c r="R50" t="n">
-        <v>6503091</v>
+        <v>6502991</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6606,11 +6611,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -3029,7 +3029,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825623</v>
+        <v>119825611</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3081,17 +3081,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 780 m, Ög</t>
+          <t>Skrikhult SSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558951</v>
+        <v>558952</v>
       </c>
       <c r="R22" t="n">
-        <v>6503018</v>
+        <v>6503001</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119825631</v>
+        <v>119825673</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3198,24 +3198,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 760 m, Ög</t>
+          <t>Skrikhult SSO-S 790 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558919</v>
+        <v>558897</v>
       </c>
       <c r="R23" t="n">
-        <v>6503036</v>
+        <v>6502998</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3245,6 +3245,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,7 +3282,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119825611</v>
+        <v>119825623</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3312,7 +3317,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3329,17 +3334,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 805 m, Ög</t>
+          <t>Skrikhult SSO 780 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558952</v>
+        <v>558951</v>
       </c>
       <c r="R24" t="n">
-        <v>6503001</v>
+        <v>6503018</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3401,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119825673</v>
+        <v>119825631</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3436,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3446,24 +3451,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 790 m, Ög</t>
+          <t>Skrikhult SSO 760 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558897</v>
+        <v>558919</v>
       </c>
       <c r="R25" t="n">
-        <v>6502998</v>
+        <v>6503036</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3493,11 +3498,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119832201</v>
+        <v>119834421</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3582,17 +3582,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 760 m, Ög</t>
+          <t>Skrikhult S 755 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558855</v>
+        <v>558820</v>
       </c>
       <c r="R26" t="n">
-        <v>6503015</v>
+        <v>6503011</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834539</v>
+        <v>119834482</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3706,14 +3706,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skrikhult S 795 m, Ög</t>
+          <t>Skrikhult S 770 m, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558829</v>
+        <v>558820</v>
       </c>
       <c r="R27" t="n">
-        <v>6502974</v>
+        <v>6502998</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834421</v>
+        <v>119832201</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3830,17 +3830,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrikhult S 755 m, Ög</t>
+          <t>Skrikhult SSO-S 760 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558820</v>
+        <v>558855</v>
       </c>
       <c r="R28" t="n">
-        <v>6503011</v>
+        <v>6503015</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834482</v>
+        <v>119834539</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3954,14 +3954,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrikhult S 770 m, Ög</t>
+          <t>Skrikhult S 795 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558820</v>
+        <v>558829</v>
       </c>
       <c r="R29" t="n">
-        <v>6502998</v>
+        <v>6502974</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119876427</v>
+        <v>119875457</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4078,14 +4078,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558979</v>
+        <v>558718</v>
       </c>
       <c r="R30" t="n">
-        <v>6503050</v>
+        <v>6503026</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4118,6 +4118,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4150,7 +4155,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875457</v>
+        <v>119876386</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4185,7 +4190,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4202,17 +4207,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558718</v>
+        <v>558812</v>
       </c>
       <c r="R31" t="n">
-        <v>6503026</v>
+        <v>6503062</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4242,11 +4247,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119876406</v>
+        <v>119876379</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4324,21 +4324,21 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558907</v>
+        <v>558791</v>
       </c>
       <c r="R32" t="n">
-        <v>6503088</v>
+        <v>6503087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875598</v>
+        <v>119876427</v>
       </c>
       <c r="B33" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4415,57 +4415,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558757</v>
+        <v>558979</v>
       </c>
       <c r="R33" t="n">
-        <v>6503043</v>
+        <v>6503050</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,11 +4495,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4532,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119876379</v>
+        <v>119875598</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4544,54 +4539,54 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558791</v>
+        <v>558757</v>
       </c>
       <c r="R34" t="n">
-        <v>6503087</v>
+        <v>6503043</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4624,6 +4619,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876386</v>
+        <v>119876406</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4701,21 +4701,21 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558812</v>
+        <v>558907</v>
       </c>
       <c r="R35" t="n">
-        <v>6503062</v>
+        <v>6503088</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875436</v>
+        <v>119918375</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4825,21 +4825,21 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558732</v>
+        <v>558786</v>
       </c>
       <c r="R36" t="n">
-        <v>6502967</v>
+        <v>6503023</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,6 +4887,11 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4904,10 +4909,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918419</v>
+        <v>119918517</v>
       </c>
       <c r="B37" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4916,42 +4921,54 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558834</v>
+        <v>558861</v>
       </c>
       <c r="R37" t="n">
-        <v>6503110</v>
+        <v>6503130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4999,11 +5016,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5021,10 +5033,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918403</v>
+        <v>119751705</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5033,57 +5045,57 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558834</v>
+        <v>558794</v>
       </c>
       <c r="R38" t="n">
-        <v>6503110</v>
+        <v>6502975</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5107,12 +5119,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5128,11 +5140,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5150,7 +5157,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119918328</v>
+        <v>119875436</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -5185,7 +5192,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5195,21 +5202,21 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558801</v>
+        <v>558732</v>
       </c>
       <c r="R39" t="n">
-        <v>6502991</v>
+        <v>6502967</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5236,12 +5243,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5274,7 +5281,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119918375</v>
+        <v>119918537</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -5309,7 +5316,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5326,17 +5333,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558786</v>
+        <v>558947</v>
       </c>
       <c r="R40" t="n">
-        <v>6503023</v>
+        <v>6503121</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5381,11 +5388,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5403,10 +5405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119751705</v>
+        <v>119918403</v>
       </c>
       <c r="B41" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5415,57 +5417,57 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558794</v>
+        <v>558834</v>
       </c>
       <c r="R41" t="n">
-        <v>6502975</v>
+        <v>6503110</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5489,12 +5491,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5510,6 +5512,11 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5527,10 +5534,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918517</v>
+        <v>119918419</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5539,54 +5546,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558861</v>
+        <v>558834</v>
       </c>
       <c r="R42" t="n">
-        <v>6503130</v>
+        <v>6503110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5634,6 +5629,11 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918537</v>
+        <v>119918328</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5703,17 +5703,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558947</v>
+        <v>558801</v>
       </c>
       <c r="R43" t="n">
-        <v>6503121</v>
+        <v>6502991</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119964721</v>
+        <v>119966093</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5956,17 +5956,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558950</v>
+        <v>559098</v>
       </c>
       <c r="R45" t="n">
-        <v>6503096</v>
+        <v>6503022</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966093</v>
+        <v>119964682</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6040,57 +6040,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>559098</v>
+        <v>558954</v>
       </c>
       <c r="R46" t="n">
-        <v>6503022</v>
+        <v>6503037</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6152,10 +6147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119964682</v>
+        <v>119964721</v>
       </c>
       <c r="B47" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6164,25 +6159,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6192,21 +6187,26 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558954</v>
+        <v>558950</v>
       </c>
       <c r="R47" t="n">
-        <v>6503037</v>
+        <v>6503096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964711</v>
+        <v>119966290</v>
       </c>
       <c r="B48" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6283,54 +6283,54 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558933</v>
+        <v>559102</v>
       </c>
       <c r="R48" t="n">
-        <v>6503091</v>
+        <v>6502963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966290</v>
+        <v>119966118</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6440,24 +6440,24 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559102</v>
+        <v>559095</v>
       </c>
       <c r="R49" t="n">
-        <v>6502963</v>
+        <v>6502991</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966118</v>
+        <v>119964711</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>559095</v>
+        <v>558933</v>
       </c>
       <c r="R50" t="n">
-        <v>6502991</v>
+        <v>6503091</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -4155,7 +4155,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119876386</v>
+        <v>119876427</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4207,17 +4207,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558812</v>
+        <v>558979</v>
       </c>
       <c r="R31" t="n">
-        <v>6503062</v>
+        <v>6503050</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119876379</v>
+        <v>119875598</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4291,54 +4291,54 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558791</v>
+        <v>558757</v>
       </c>
       <c r="R32" t="n">
-        <v>6503087</v>
+        <v>6503043</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4371,6 +4371,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4403,7 +4408,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876427</v>
+        <v>119876379</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -4438,7 +4443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4455,17 +4460,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558979</v>
+        <v>558791</v>
       </c>
       <c r="R33" t="n">
-        <v>6503050</v>
+        <v>6503087</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4527,10 +4532,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875598</v>
+        <v>119876406</v>
       </c>
       <c r="B34" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4539,35 +4544,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4579,14 +4584,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558757</v>
+        <v>558907</v>
       </c>
       <c r="R34" t="n">
-        <v>6503043</v>
+        <v>6503088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4619,11 +4624,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876406</v>
+        <v>119876386</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4701,21 +4701,21 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558907</v>
+        <v>558812</v>
       </c>
       <c r="R35" t="n">
-        <v>6503088</v>
+        <v>6503062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119918375</v>
+        <v>119875436</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4825,21 +4825,21 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558786</v>
+        <v>558732</v>
       </c>
       <c r="R36" t="n">
-        <v>6503023</v>
+        <v>6502967</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,11 +4887,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4909,7 +4904,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918517</v>
+        <v>119918375</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4944,7 +4939,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4954,21 +4949,21 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558861</v>
+        <v>558786</v>
       </c>
       <c r="R37" t="n">
-        <v>6503130</v>
+        <v>6503023</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5016,6 +5011,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5033,10 +5033,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119751705</v>
+        <v>119918328</v>
       </c>
       <c r="B38" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5045,35 +5045,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5085,17 +5085,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558794</v>
+        <v>558801</v>
       </c>
       <c r="R38" t="n">
-        <v>6502975</v>
+        <v>6502991</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5119,12 +5119,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875436</v>
+        <v>119751705</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5169,57 +5169,57 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558732</v>
+        <v>558794</v>
       </c>
       <c r="R39" t="n">
-        <v>6502967</v>
+        <v>6502975</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119918537</v>
+        <v>119918419</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5293,57 +5293,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558947</v>
+        <v>558834</v>
       </c>
       <c r="R40" t="n">
-        <v>6503121</v>
+        <v>6503110</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5388,6 +5376,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5405,7 +5398,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918403</v>
+        <v>119918537</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -5440,7 +5433,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5450,24 +5443,24 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558834</v>
+        <v>558947</v>
       </c>
       <c r="R41" t="n">
-        <v>6503110</v>
+        <v>6503121</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5512,11 +5505,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5534,10 +5522,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918419</v>
+        <v>119918403</v>
       </c>
       <c r="B42" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5546,30 +5534,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918328</v>
+        <v>119918517</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5696,21 +5696,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558801</v>
+        <v>558861</v>
       </c>
       <c r="R43" t="n">
-        <v>6502991</v>
+        <v>6503130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119964704</v>
+        <v>119964682</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,25 +5787,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5815,26 +5815,21 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558933</v>
+        <v>558954</v>
       </c>
       <c r="R44" t="n">
-        <v>6503091</v>
+        <v>6503037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5867,11 +5862,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5904,7 +5894,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966093</v>
+        <v>119964704</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5939,7 +5929,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5956,17 +5946,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559098</v>
+        <v>558933</v>
       </c>
       <c r="R45" t="n">
-        <v>6503022</v>
+        <v>6503091</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5996,6 +5986,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6028,10 +6023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119964682</v>
+        <v>119966093</v>
       </c>
       <c r="B46" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6040,52 +6035,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558954</v>
+        <v>559098</v>
       </c>
       <c r="R46" t="n">
-        <v>6503037</v>
+        <v>6503022</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119964721</v>
+        <v>119966290</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6192,21 +6192,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558950</v>
+        <v>559102</v>
       </c>
       <c r="R47" t="n">
-        <v>6503096</v>
+        <v>6502963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966290</v>
+        <v>119964711</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6283,54 +6283,54 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>559102</v>
+        <v>558933</v>
       </c>
       <c r="R48" t="n">
-        <v>6502963</v>
+        <v>6503091</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966118</v>
+        <v>119964721</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6447,17 +6447,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559095</v>
+        <v>558950</v>
       </c>
       <c r="R49" t="n">
-        <v>6502991</v>
+        <v>6503096</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119964711</v>
+        <v>119966118</v>
       </c>
       <c r="B50" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558933</v>
+        <v>559095</v>
       </c>
       <c r="R50" t="n">
-        <v>6503091</v>
+        <v>6502991</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -4026,10 +4026,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875457</v>
+        <v>119875598</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4038,57 +4038,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrikhult S 740 m, Ög</t>
+          <t>Skrikhult S 725 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558718</v>
+        <v>558757</v>
       </c>
       <c r="R30" t="n">
-        <v>6503026</v>
+        <v>6503043</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Något spridda</t>
+          <t>Ca 50 plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4155,7 +4155,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119876427</v>
+        <v>119876406</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4200,24 +4200,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 770 m, Ög</t>
+          <t>Skrikhult SSO 710 m, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558979</v>
+        <v>558907</v>
       </c>
       <c r="R31" t="n">
-        <v>6503050</v>
+        <v>6503088</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875598</v>
+        <v>119875457</v>
       </c>
       <c r="B32" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4291,57 +4291,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrikhult S 725 m, Ög</t>
+          <t>Skrikhult S 740 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558757</v>
+        <v>558718</v>
       </c>
       <c r="R32" t="n">
-        <v>6503043</v>
+        <v>6503026</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 50 plantor</t>
+          <t>Något spridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4408,7 +4408,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119876379</v>
+        <v>119876427</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4460,17 +4460,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrikhult S 685 m, Ög</t>
+          <t>Skrikhult SSO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558791</v>
+        <v>558979</v>
       </c>
       <c r="R33" t="n">
-        <v>6503087</v>
+        <v>6503050</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119876406</v>
+        <v>119876386</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4577,21 +4577,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 710 m, Ög</t>
+          <t>Skrikhult S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558907</v>
+        <v>558812</v>
       </c>
       <c r="R34" t="n">
-        <v>6503088</v>
+        <v>6503062</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119876386</v>
+        <v>119876379</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4708,14 +4708,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrikhult S 705 m, Ög</t>
+          <t>Skrikhult S 685 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558812</v>
+        <v>558791</v>
       </c>
       <c r="R35" t="n">
-        <v>6503062</v>
+        <v>6503087</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875436</v>
+        <v>119918517</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4832,14 +4832,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558732</v>
+        <v>558861</v>
       </c>
       <c r="R36" t="n">
-        <v>6502967</v>
+        <v>6503130</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4904,10 +4904,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119918375</v>
+        <v>119751705</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4916,35 +4916,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4956,17 +4956,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558786</v>
+        <v>558794</v>
       </c>
       <c r="R37" t="n">
-        <v>6503023</v>
+        <v>6502975</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5011,11 +5011,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5033,7 +5028,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918328</v>
+        <v>119918375</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -5068,7 +5063,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5085,14 +5080,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558801</v>
+        <v>558786</v>
       </c>
       <c r="R38" t="n">
-        <v>6502991</v>
+        <v>6503023</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5140,6 +5135,11 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119751705</v>
+        <v>119918328</v>
       </c>
       <c r="B39" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5169,35 +5169,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5209,17 +5209,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558794</v>
+        <v>558801</v>
       </c>
       <c r="R39" t="n">
-        <v>6502975</v>
+        <v>6502991</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119918419</v>
+        <v>119918403</v>
       </c>
       <c r="B40" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5293,30 +5293,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -5398,7 +5410,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918537</v>
+        <v>119875436</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -5433,7 +5445,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5443,24 +5455,24 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 690 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558947</v>
+        <v>558732</v>
       </c>
       <c r="R41" t="n">
-        <v>6503121</v>
+        <v>6502967</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5484,12 +5496,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5522,10 +5534,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918403</v>
+        <v>119918419</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5534,42 +5546,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119918517</v>
+        <v>119918537</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5696,24 +5696,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult SSO 690 m, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558861</v>
+        <v>558947</v>
       </c>
       <c r="R43" t="n">
-        <v>6503130</v>
+        <v>6503121</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119964682</v>
+        <v>119964721</v>
       </c>
       <c r="B44" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,25 +5787,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5815,21 +5815,26 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558954</v>
+        <v>558950</v>
       </c>
       <c r="R44" t="n">
-        <v>6503037</v>
+        <v>6503096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5894,10 +5899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119964704</v>
+        <v>119964711</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5906,35 +5911,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5986,11 +5991,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966290</v>
+        <v>119964704</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6192,21 +6192,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559102</v>
+        <v>558933</v>
       </c>
       <c r="R47" t="n">
-        <v>6502963</v>
+        <v>6503091</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6239,6 +6239,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6271,10 +6276,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964711</v>
+        <v>119966290</v>
       </c>
       <c r="B48" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6283,54 +6288,54 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558933</v>
+        <v>559102</v>
       </c>
       <c r="R48" t="n">
-        <v>6503091</v>
+        <v>6502963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6395,10 +6400,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964721</v>
+        <v>119964682</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,25 +6412,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6435,26 +6440,21 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558950</v>
+        <v>558954</v>
       </c>
       <c r="R49" t="n">
-        <v>6503096</v>
+        <v>6503037</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -5410,10 +5410,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119875436</v>
+        <v>119918419</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5422,54 +5422,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558732</v>
+        <v>558834</v>
       </c>
       <c r="R41" t="n">
-        <v>6502967</v>
+        <v>6503110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5496,12 +5484,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5517,6 +5505,11 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5534,10 +5527,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119918419</v>
+        <v>119875436</v>
       </c>
       <c r="B42" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5546,42 +5539,54 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558834</v>
+        <v>558732</v>
       </c>
       <c r="R42" t="n">
-        <v>6503110</v>
+        <v>6502967</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5608,12 +5613,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5629,11 +5634,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -4780,7 +4780,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119918517</v>
+        <v>119918375</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4825,21 +4825,21 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 650 m, Ög</t>
+          <t>Skrikhult S 745 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558861</v>
+        <v>558786</v>
       </c>
       <c r="R36" t="n">
-        <v>6503130</v>
+        <v>6503023</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4887,6 +4887,11 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4904,10 +4909,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119751705</v>
+        <v>119875436</v>
       </c>
       <c r="B37" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4916,57 +4921,57 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 780 m, Ög</t>
+          <t>Skrikhult S 805 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558794</v>
+        <v>558732</v>
       </c>
       <c r="R37" t="n">
-        <v>6502975</v>
+        <v>6502967</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4990,12 +4995,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5028,10 +5033,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119918375</v>
+        <v>119751705</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5040,35 +5045,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5080,17 +5085,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrikhult S 745 m, Ög</t>
+          <t>Skrikhult SSO-S 780 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558786</v>
+        <v>558794</v>
       </c>
       <c r="R38" t="n">
-        <v>6503023</v>
+        <v>6502975</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5114,12 +5119,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5135,11 +5140,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Tall, gran och några björkar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119918328</v>
+        <v>119918419</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5169,54 +5169,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrikhult S 775 m, Ög</t>
+          <t>Skrikhult SSO-S 665 m, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558801</v>
+        <v>558834</v>
       </c>
       <c r="R39" t="n">
-        <v>6502991</v>
+        <v>6503110</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5252,11 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5410,10 +5403,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119918419</v>
+        <v>119918328</v>
       </c>
       <c r="B41" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5422,42 +5415,54 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrikhult SSO-S 665 m, Ög</t>
+          <t>Skrikhult S 775 m, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558834</v>
+        <v>558801</v>
       </c>
       <c r="R41" t="n">
-        <v>6503110</v>
+        <v>6502991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Barrskog och några lövträd</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119875436</v>
+        <v>119918517</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5579,14 +5579,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrikhult S 805 m, Ög</t>
+          <t>Skrikhult SSO-S 650 m, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558732</v>
+        <v>558861</v>
       </c>
       <c r="R42" t="n">
-        <v>6502967</v>
+        <v>6503130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5775,7 +5775,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119964721</v>
+        <v>119966093</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5827,17 +5827,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558950</v>
+        <v>559098</v>
       </c>
       <c r="R44" t="n">
-        <v>6503096</v>
+        <v>6503022</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119964711</v>
+        <v>119964704</v>
       </c>
       <c r="B45" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5911,35 +5911,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5991,6 +5991,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6023,10 +6028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966093</v>
+        <v>119964682</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6035,57 +6040,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>559098</v>
+        <v>558954</v>
       </c>
       <c r="R46" t="n">
-        <v>6503022</v>
+        <v>6503037</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119964704</v>
+        <v>119966290</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6192,21 +6192,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558933</v>
+        <v>559102</v>
       </c>
       <c r="R47" t="n">
-        <v>6503091</v>
+        <v>6502963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6239,11 +6239,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6276,7 +6271,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966290</v>
+        <v>119966118</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -6311,7 +6306,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6321,24 +6316,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>559102</v>
+        <v>559095</v>
       </c>
       <c r="R48" t="n">
-        <v>6502963</v>
+        <v>6502991</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6400,10 +6395,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964682</v>
+        <v>119964721</v>
       </c>
       <c r="B49" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6412,25 +6407,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6440,21 +6435,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558954</v>
+        <v>558950</v>
       </c>
       <c r="R49" t="n">
-        <v>6503037</v>
+        <v>6503096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966118</v>
+        <v>119964711</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>559095</v>
+        <v>558933</v>
       </c>
       <c r="R50" t="n">
-        <v>6502991</v>
+        <v>6503091</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -5775,7 +5775,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966093</v>
+        <v>119964704</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5827,17 +5827,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrikhult SO 845 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559098</v>
+        <v>558933</v>
       </c>
       <c r="R44" t="n">
-        <v>6503022</v>
+        <v>6503091</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5867,6 +5867,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5899,10 +5904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119964704</v>
+        <v>119964682</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5911,25 +5916,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5939,26 +5944,21 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SSO 772 m, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558933</v>
+        <v>558954</v>
       </c>
       <c r="R45" t="n">
-        <v>6503091</v>
+        <v>6503037</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5991,11 +5991,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fler kan finnas under granriset från underröjningen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6028,10 +6023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119964682</v>
+        <v>119964711</v>
       </c>
       <c r="B46" t="n">
-        <v>91203</v>
+        <v>105032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6044,45 +6039,50 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 772 m, Ög</t>
+          <t>Skrikhult SSO 712 m, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558954</v>
+        <v>558933</v>
       </c>
       <c r="R46" t="n">
-        <v>6503037</v>
+        <v>6503091</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966118</v>
+        <v>119964721</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6323,17 +6323,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 865 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>559095</v>
+        <v>558950</v>
       </c>
       <c r="R48" t="n">
-        <v>6502991</v>
+        <v>6503096</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119964721</v>
+        <v>119966118</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6447,17 +6447,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO-S 865 m, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558950</v>
+        <v>559095</v>
       </c>
       <c r="R49" t="n">
-        <v>6503096</v>
+        <v>6502991</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119964711</v>
+        <v>119966093</v>
       </c>
       <c r="B50" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6531,35 +6531,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6571,17 +6571,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 712 m, Ög</t>
+          <t>Skrikhult SO 845 m, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558933</v>
+        <v>559098</v>
       </c>
       <c r="R50" t="n">
-        <v>6503091</v>
+        <v>6503022</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2024 artfynd.xlsx
+++ b/artfynd/A 28424-2024 artfynd.xlsx
@@ -6147,7 +6147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966290</v>
+        <v>119964721</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6192,21 +6192,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 905 m, Ög</t>
+          <t>Skrikhult SSO 717 m, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559102</v>
+        <v>558950</v>
       </c>
       <c r="R47" t="n">
-        <v>6502963</v>
+        <v>6503096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119964721</v>
+        <v>119966290</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6316,21 +6316,21 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skrikhult SSO 717 m, Ög</t>
+          <t>Skrikhult SO-S 905 m, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558950</v>
+        <v>559102</v>
       </c>
       <c r="R48" t="n">
-        <v>6503096</v>
+        <v>6502963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
